--- a/wbs-tasks-vi.xlsx
+++ b/wbs-tasks-vi.xlsx
@@ -18,9 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -230,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -343,6 +344,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1566,7 +1570,7 @@
       </c>
       <c r="N17" s="37" t="inlineStr">
         <is>
-          <t>📄 .opencode/skills/ (40 folders)
+          <t>📄 .opencode/skills/ (48 folders)
 📄 settings/pages/skills-view.tsx
 📄 apps/server/src/skill-hub.ts</t>
         </is>
@@ -2016,12 +2020,12 @@
       </c>
       <c r="B26" s="37" t="inlineStr">
         <is>
-          <t>Phase 3: Scheduled Tasks ❌ NONE</t>
-        </is>
-      </c>
-      <c r="C26" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>Phase 3: Scheduled Tasks ✅ IN PROGRESS (83%)</t>
+        </is>
+      </c>
+      <c r="C26" s="38" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="D26" s="37" t="inlineStr">
@@ -2034,14 +2038,22 @@
           <t>Nhân</t>
         </is>
       </c>
-      <c r="F26" s="37" t="inlineStr"/>
+      <c r="F26" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
       <c r="G26" s="37" t="inlineStr"/>
-      <c r="H26" s="37" t="inlineStr"/>
+      <c r="H26" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I26" s="37" t="n">
         <v>38</v>
       </c>
       <c r="J26" s="37" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="K26" s="37" t="inlineStr"/>
       <c r="L26" s="37" t="inlineStr">
@@ -2051,12 +2063,16 @@
       </c>
       <c r="M26" s="37" t="inlineStr">
         <is>
-          <t>MỚI — cần xây từ đầu</t>
+          <t>S1-S5 done, còn E2E test</t>
         </is>
       </c>
       <c r="N26" s="37" t="inlineStr">
         <is>
-          <t>🔗 aionui:packages/desktop/src/renderer/pages/cron/ (toàn bộ folder AionUi)</t>
+          <t>📄 apps/server/src/scheduled/repo.ts
+📄 apps/server/src/scheduled/scheduler.ts
+📄 apps/server/src/scheduled/runner.ts
+📄 apps/server/src/routes/scheduled.ts
+📄 apps/app/.../scheduled/scheduled-tasks-view.tsx</t>
         </is>
       </c>
     </row>
@@ -2071,9 +2087,9 @@
           <t>DB migration: cron_jobs table</t>
         </is>
       </c>
-      <c r="C27" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C27" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D27" s="37" t="inlineStr">
@@ -2088,12 +2104,16 @@
       </c>
       <c r="F27" s="37" t="inlineStr"/>
       <c r="G27" s="37" t="inlineStr"/>
-      <c r="H27" s="37" t="inlineStr"/>
+      <c r="H27" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I27" s="37" t="n">
         <v>2</v>
       </c>
       <c r="J27" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27" s="37" t="inlineStr"/>
       <c r="L27" s="37" t="inlineStr">
@@ -2103,13 +2123,12 @@
       </c>
       <c r="M27" s="37" t="inlineStr">
         <is>
-          <t>Schema: id, user_id, cron_expr, prompt, enabled...</t>
+          <t>schema + repo với CREATE TABLE IF NOT EXISTS</t>
         </is>
       </c>
       <c r="N27" s="37" t="inlineStr">
         <is>
-          <t>🔗 aionui:/cron/cronUtils.ts
-📄 ee/packages/den-db/drizzle/ (pattern migration)</t>
+          <t>📄 apps/server/src/scheduled/repo.ts</t>
         </is>
       </c>
     </row>
@@ -2124,9 +2143,9 @@
           <t>Cron runner service (croner)</t>
         </is>
       </c>
-      <c r="C28" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D28" s="37" t="inlineStr">
@@ -2141,12 +2160,16 @@
       </c>
       <c r="F28" s="37" t="inlineStr"/>
       <c r="G28" s="37" t="inlineStr"/>
-      <c r="H28" s="37" t="inlineStr"/>
+      <c r="H28" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I28" s="37" t="n">
         <v>8</v>
       </c>
       <c r="J28" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28" s="37" t="inlineStr">
         <is>
@@ -2160,12 +2183,12 @@
       </c>
       <c r="M28" s="37" t="inlineStr">
         <is>
-          <t>Bun server + croner npm</t>
+          <t>In-process cron scheduler + test</t>
         </is>
       </c>
       <c r="N28" s="37" t="inlineStr">
         <is>
-          <t>🔗 aionui:packages/desktop/src/renderer/pages/cron/components/CronJobManager.tsx</t>
+          <t>📄 apps/server/src/scheduled/scheduler.ts</t>
         </is>
       </c>
     </row>
@@ -2180,9 +2203,9 @@
           <t>CRUD API routes</t>
         </is>
       </c>
-      <c r="C29" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C29" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D29" s="37" t="inlineStr">
@@ -2197,12 +2220,16 @@
       </c>
       <c r="F29" s="37" t="inlineStr"/>
       <c r="G29" s="37" t="inlineStr"/>
-      <c r="H29" s="37" t="inlineStr"/>
+      <c r="H29" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I29" s="37" t="n">
         <v>4</v>
       </c>
       <c r="J29" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K29" s="37" t="inlineStr">
         <is>
@@ -2216,13 +2243,12 @@
       </c>
       <c r="M29" s="37" t="inlineStr">
         <is>
-          <t>GET/POST/PUT/DELETE /api/cron</t>
+          <t>GET/POST/PUT/DELETE /api/scheduled + /api/scheduled/:id/run</t>
         </is>
       </c>
       <c r="N29" s="37" t="inlineStr">
         <is>
-          <t>🔗 aionui:/cron/useCronJobs.ts
-📄 apps/server/src/routes/sessions.ts (pattern)</t>
+          <t>📄 apps/server/src/routes/scheduled.ts</t>
         </is>
       </c>
     </row>
@@ -2237,9 +2263,9 @@
           <t>Settings UI page</t>
         </is>
       </c>
-      <c r="C30" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D30" s="37" t="inlineStr">
@@ -2254,12 +2280,16 @@
       </c>
       <c r="F30" s="37" t="inlineStr"/>
       <c r="G30" s="37" t="inlineStr"/>
-      <c r="H30" s="37" t="inlineStr"/>
+      <c r="H30" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I30" s="37" t="n">
         <v>12</v>
       </c>
       <c r="J30" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30" s="37" t="inlineStr">
         <is>
@@ -2273,13 +2303,13 @@
       </c>
       <c r="M30" s="37" t="inlineStr">
         <is>
-          <t>Create/edit/enable/disable</t>
+          <t>List + toggle enable/disable (chưa có create/edit dialog)</t>
         </is>
       </c>
       <c r="N30" s="37" t="inlineStr">
         <is>
-          <t>🔗 aionui:/cron/ScheduledTasksPage/index.tsx
-🔗 aionui:/cron/ScheduledTasksPage/CreateTaskDialog.tsx</t>
+          <t>📄 apps/app/src/react-app/domains/settings/scheduled/scheduled-tasks-view.tsx
+📄 apps/app/.../sidebar/quick-actions-group.tsx</t>
         </is>
       </c>
     </row>
@@ -2294,9 +2324,9 @@
           <t>Execution engine + conversation relay</t>
         </is>
       </c>
-      <c r="C31" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C31" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D31" s="37" t="inlineStr">
@@ -2311,12 +2341,16 @@
       </c>
       <c r="F31" s="37" t="inlineStr"/>
       <c r="G31" s="37" t="inlineStr"/>
-      <c r="H31" s="37" t="inlineStr"/>
+      <c r="H31" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I31" s="37" t="n">
         <v>8</v>
       </c>
       <c r="J31" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31" s="37" t="inlineStr">
         <is>
@@ -2330,12 +2364,12 @@
       </c>
       <c r="M31" s="37" t="inlineStr">
         <is>
-          <t>Gửi prompt đúng lịch</t>
+          <t>Create session, gửi prompt, skip-overlap, timeout</t>
         </is>
       </c>
       <c r="N31" s="37" t="inlineStr">
         <is>
-          <t>🔗 aionui:/cron/components/CronJobManager.tsx</t>
+          <t>📄 apps/server/src/scheduled/runner.ts</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3149,12 @@
       </c>
       <c r="B46" s="37" t="inlineStr">
         <is>
-          <t>Phase 6: Version History ⚠️ EARLY (5%)</t>
-        </is>
-      </c>
-      <c r="C46" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>Phase 6: Version History ✅ DONE (100%)</t>
+        </is>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D46" s="37" t="inlineStr">
@@ -3135,12 +3169,16 @@
       </c>
       <c r="F46" s="37" t="inlineStr"/>
       <c r="G46" s="37" t="inlineStr"/>
-      <c r="H46" s="37" t="inlineStr"/>
+      <c r="H46" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I46" s="37" t="n">
         <v>26</v>
       </c>
       <c r="J46" s="37" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K46" s="37" t="inlineStr"/>
       <c r="L46" s="37" t="inlineStr">
@@ -3150,13 +3188,15 @@
       </c>
       <c r="M46" s="37" t="inlineStr">
         <is>
-          <t>PRIORITY CAO NHẤT — building blocks có sẵn</t>
+          <t>Hoàn thành — snapshot + API + UI + diff</t>
         </is>
       </c>
       <c r="N46" s="37" t="inlineStr">
         <is>
-          <t>📄 apps/server/src/services/file-sessions.ts
-📄 apps/server/src/services/audit.ts
+          <t>📄 apps/server/src/file-snapshots.ts
+📄 apps/server/src/snapshot-middleware.ts
+📄 apps/server/src/routes/history.ts
+📄 apps/app/.../file-history-panel.tsx
 📄 apps/app/.../viewers/diff-viewer.tsx</t>
         </is>
       </c>
@@ -3340,9 +3380,9 @@
           <t>DB migration: file_snapshots</t>
         </is>
       </c>
-      <c r="C50" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C50" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D50" s="37" t="inlineStr">
@@ -3357,12 +3397,16 @@
       </c>
       <c r="F50" s="37" t="inlineStr"/>
       <c r="G50" s="37" t="inlineStr"/>
-      <c r="H50" s="37" t="inlineStr"/>
+      <c r="H50" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I50" s="37" t="n">
         <v>2</v>
       </c>
       <c r="J50" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K50" s="37" t="inlineStr"/>
       <c r="L50" s="37" t="inlineStr">
@@ -3372,12 +3416,12 @@
       </c>
       <c r="M50" s="37" t="inlineStr">
         <is>
-          <t>Schema: id, workspace_id, file_path, content_hash, content, created_at, trigger</t>
+          <t>file-snapshots.ts với CREATE TABLE IF NOT EXISTS</t>
         </is>
       </c>
       <c r="N50" s="37" t="inlineStr">
         <is>
-          <t>🔗 aionui:.../hooks/usePreviewHistory.ts (schema pattern)</t>
+          <t>📄 apps/server/src/file-snapshots.ts</t>
         </is>
       </c>
     </row>
@@ -3392,9 +3436,9 @@
           <t>Auto-snapshot on save middleware</t>
         </is>
       </c>
-      <c r="C51" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C51" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D51" s="37" t="inlineStr">
@@ -3409,12 +3453,16 @@
       </c>
       <c r="F51" s="37" t="inlineStr"/>
       <c r="G51" s="37" t="inlineStr"/>
-      <c r="H51" s="37" t="inlineStr"/>
+      <c r="H51" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I51" s="37" t="n">
         <v>4</v>
       </c>
       <c r="J51" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K51" s="37" t="inlineStr">
         <is>
@@ -3428,12 +3476,12 @@
       </c>
       <c r="M51" s="37" t="inlineStr">
         <is>
-          <t>Snapshot content trước ghi đè</t>
+          <t>snapshot-middleware.ts + test</t>
         </is>
       </c>
       <c r="N51" s="37" t="inlineStr">
         <is>
-          <t>🔗 aionui:packages/desktop/src/process/utils/snapshotService.ts (ước lượng)</t>
+          <t>📄 apps/server/src/snapshot-middleware.ts</t>
         </is>
       </c>
     </row>
@@ -3448,9 +3496,9 @@
           <t>History API route</t>
         </is>
       </c>
-      <c r="C52" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C52" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D52" s="37" t="inlineStr">
@@ -3465,12 +3513,16 @@
       </c>
       <c r="F52" s="37" t="inlineStr"/>
       <c r="G52" s="37" t="inlineStr"/>
-      <c r="H52" s="37" t="inlineStr"/>
+      <c r="H52" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I52" s="37" t="n">
         <v>4</v>
       </c>
       <c r="J52" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K52" s="37" t="inlineStr">
         <is>
@@ -3484,12 +3536,12 @@
       </c>
       <c r="M52" s="37" t="inlineStr">
         <is>
-          <t>GET list + POST restore</t>
+          <t>GET list/diff/content + POST restore</t>
         </is>
       </c>
       <c r="N52" s="37" t="inlineStr">
         <is>
-          <t>📄 apps/server/src/routes/files.ts (pattern)</t>
+          <t>📄 apps/server/src/routes/history.ts</t>
         </is>
       </c>
     </row>
@@ -3504,9 +3556,9 @@
           <t>History UI dropdown</t>
         </is>
       </c>
-      <c r="C53" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C53" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D53" s="37" t="inlineStr">
@@ -3521,12 +3573,16 @@
       </c>
       <c r="F53" s="37" t="inlineStr"/>
       <c r="G53" s="37" t="inlineStr"/>
-      <c r="H53" s="37" t="inlineStr"/>
+      <c r="H53" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I53" s="37" t="n">
         <v>8</v>
       </c>
       <c r="J53" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K53" s="37" t="inlineStr">
         <is>
@@ -3540,12 +3596,13 @@
       </c>
       <c r="M53" s="37" t="inlineStr">
         <is>
-          <t>Danh sách version + restore button</t>
+          <t>FileHistoryPanel popover — History + All Changes tabs</t>
         </is>
       </c>
       <c r="N53" s="37" t="inlineStr">
         <is>
-          <t>🔗 aionui:.../Preview/components/.../PreviewHistoryDropdown.tsx</t>
+          <t>📄 apps/app/src/react-app/domains/session/artifacts/file-history-panel.tsx
+📄 apps/app/.../hooks/use-file-history.ts</t>
         </is>
       </c>
     </row>
@@ -3560,9 +3617,9 @@
           <t>Diff compare 2 versions</t>
         </is>
       </c>
-      <c r="C54" s="41" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="C54" s="40" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="D54" s="37" t="inlineStr">
@@ -3577,12 +3634,16 @@
       </c>
       <c r="F54" s="37" t="inlineStr"/>
       <c r="G54" s="37" t="inlineStr"/>
-      <c r="H54" s="37" t="inlineStr"/>
+      <c r="H54" s="37" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="I54" s="37" t="n">
         <v>4</v>
       </c>
       <c r="J54" s="37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K54" s="37" t="inlineStr">
         <is>
@@ -3596,12 +3657,13 @@
       </c>
       <c r="M54" s="37" t="inlineStr">
         <is>
-          <t>So sánh bất kỳ 2 snapshot</t>
+          <t>Server unified-diff + API endpoint</t>
         </is>
       </c>
       <c r="N54" s="37" t="inlineStr">
         <is>
-          <t>📄 diff-viewer.tsx (đã có) + API mới</t>
+          <t>📄 apps/server/src/diff.ts
+📄 apps/server/src/routes/history.ts (diff endpoint)</t>
         </is>
       </c>
     </row>
@@ -7255,12 +7317,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>❌ NONE (0%)</t>
+          <t>✅ IN PROGRESS (83%)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0/7</t>
+          <t>5/6</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -7315,12 +7377,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>⚠️ EARLY (5%)</t>
+          <t>✅ DONE (100%)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>8/8</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -7462,7 +7524,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>55/99</t>
+          <t>66/99</t>
         </is>
       </c>
       <c r="D23" t="n">
